--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0094.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0094.xlsx
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Ta không quan tâm dù cô ấy chỉ muốn ta làm lao công, ta sẽ làm bất cứ điều gì để được vào đội nghiên cứu của Giáo sư Mornye!</t>
+          <t>Tao không quan tâm dù cô ấy chỉ muốn tao làm lao công, tao sẽ làm bất cứ điều gì để được vào đội nghiên cứu của Giáo sư Mornye!</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Nếu Hội Hoàng Gia đồng ý, tôi rất muốn dựng trại ở Rừng Bjartr để nghiên cứu chúng thật kỹ...</t>
+          <t>Nếu Hội Hoàng Gia đồng ý, tôi rất muốn dựng trại ở Bjartr Woods để nghiên cứu chúng thật kỹ...</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Ta đã thử ổn định tình trạng bằng Cassette. Nó có giúp, nhưng không chữa khỏi hoàn toàn. Ráng ghi lại đoạn nhật ký này.</t>
+          <t>Tao đã thử ổn định tình trạng bằng Cassette. Nó có giúp, nhưng không chữa khỏi hoàn toàn. Ráng ghi lại đoạn nhật ký này.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>...Ta phải nhắc lại bao nhiêu lần nữa đây? Ở vùng băng giá này, ai sống thì sống, ai chết thì chết. Chẳng ai rảnh mà dắt tay cậu đâu.</t>
+          <t>...Tao phải nhắc lại bao nhiêu lần nữa đây? Ở vùng băng giá này, ai sống thì sống, ai chết thì chết. Chẳng ai rảnh mà dắt tay cậu đâu.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Thật khó tin... Ngày trước ta phải chen chúc trong một căn phòng với tám người khác cơ!</t>
+          <t>Thật khó tin... Ngày trước tao phải chen chúc trong một căn phòng với tám người khác cơ!</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Ta nghe nói có một học sinh chuyển đến từ Bờ Đen. Không biết có cơ hội nào để chào hỏi không nhỉ...</t>
+          <t>Tao nghe nói có một học sinh chuyển đến từ Bờ Đen. Không biết có cơ hội nào để chào hỏi không nhỉ...</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Đặt cược xem ai giành được ngân sách nghiên cứu độc lập quý tới đi. Ta cá cả danh tiếng của giáo sư ta luôn!</t>
+          <t>Đặt cược xem ai giành được ngân sách nghiên cứu độc lập quý tới đi. Tao cá cả danh tiếng của giáo sư tao luôn!</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Ta vừa nghĩ ra cách mới để sửa vấn đề tụt công suất của Helios...</t>
+          <t>Tao vừa nghĩ ra cách mới để sửa vấn đề tụt công suất của Helios...</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Không phải ta đâu. Nhưng mà... ta đang tự hỏi liệu có thể làm một chút nghiên cứu thực địa ở đây cho kỳ thực tập của mình không.</t>
+          <t>Không phải tao đâu. Nhưng mà... tao đang tự hỏi liệu có thể làm một chút nghiên cứu thực địa ở đây cho kỳ thực tập của mình không.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Về Học viện ngay! Không thì ta báo lên Phòng Học vụ và thầy cô của ngươi đấy! Bán đồ ăn vặt trong trại nghiên cứu... không thể tin nổi!</t>
+          <t>Về Học viện ngay! Không thì tao báo lên Phòng Học vụ và thầy cô của mày đấy! Bán đồ ăn vặt trong trại nghiên cứu... không thể tin nổi!</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Nhẹ tay với mấy thứ đó! Đồ vật liệu cao cấp đấy! Hỏng cái gì là Giám đốc Dự án moi gan ta ra bây giờ!</t>
+          <t>Nhẹ tay với mấy thứ đó! Đồ vật liệu cao cấp đấy! Hỏng cái gì là Giám đốc Dự án moi gan tao ra bây giờ!</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Bỏ vào túi ta đi! Không có Bánh Mì Que thì làm sao mà thám hiểm cho ra hồn!</t>
+          <t>Bỏ vào túi tao đi! Không có Bánh Mì Que thì làm sao mà thám hiểm cho ra hồn!</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Cho tôi hỏi tại sao dân ngươi không định cư trong Rừng Bjartr?</t>
+          <t>Cho tôi hỏi tại sao dân ngươi không định cư trong Bjartr Woods?</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Với Soliskin, Khu Rừng Bjartr là nhà. Nơi họ nghỉ ngơi, sinh trưởng, và cuối cùng trở về với những Cây Solistrees.</t>
+          <t>Với Soliskin, Khu Bjartr Woods là nhà. Nơi họ nghỉ ngơi, sinh trưởng, và cuối cùng trở về với những Cây Solistrees.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Đêm qua ta mơ thấy ngươi đấy, bạn thân ơi...</t>
+          <t>Đêm qua tao mơ thấy mày đấy, bạn thân ơi...</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Cậu không có chế độ dọn dẹp à! Cậu hỏng từ bao giờ thế?!</t>
+          <t>Mày không có chế độ dọn dẹp à! Mày hỏng từ bao giờ thế?!</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Sao cơ?</t>
+          <t>Lại đến nữa à?</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>TARD-E còn chẳng dám bén mảng đến những trại thế này. Ngươi sợ cái gì thế?</t>
+          <t>TARD-E còn chẳng dám bén mảng đến những trại thế này. Mày sợ cái gì thế?</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>TARD-E còn chẳng dám bén mảng đến những trại thế này. Ngươi sợ cái gì thế?</t>
+          <t>TARD-E còn chẳng dám bén mảng đến những trại thế này. Mày sợ cái gì thế?</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Ta sẽ không bao giờ quên cái nhìn trên mặt nó khi đóng cánh cửa đó lại... Điên loạn. Xã hội đen. Không thể giả tạo được cái nhìn như thế...</t>
+          <t>Tao sẽ không bao giờ quên cái nhìn trên mặt nó khi đóng cánh cửa đó lại... Điên loạn. Xã hội đen. Không thể giả tạo được cái nhìn như thế...</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Ấn tượng. Một mình lao vào vùng Voidworm đang hoạt động, lại còn khiến Học viện hủy bỏ hình phạt cho cậu... Đúng là chỉ có thể là cậu, Miles.</t>
+          <t>Ấn tượng. Một mình lao vào vùng Voidworm đang hoạt động, lại còn khiến Học viện hủy bỏ hình phạt cho mày... Đúng là chỉ có thể là mày, Miles.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ganno, nhìn vào mắt ta! Trả lời ta! TẠI SAO?!</t>
+          <t>Ganno, nhìn vào mắt tao! Trả lời tao! TẠI SAO?!</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Ta!!</t>
+          <t>Tao!!</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
